--- a/code/data/coursedata.xlsx
+++ b/code/data/coursedata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MyAccount/Documents/_Development/generateCorporateCoursedata/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBB1CD-7B0C-A347-9338-913346C514A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA866E8B-5AD5-CA47-B2AC-C139CEF52FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29140" windowHeight="18980" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
+    <workbookView xWindow="17060" yWindow="-21000" windowWidth="29840" windowHeight="21000" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="456">
   <si>
     <t>Description</t>
   </si>
@@ -1392,6 +1392,18 @@
   </si>
   <si>
     <t>Education &amp; Public Sector: Education, Government Services, Non-Profit organizations </t>
+  </si>
+  <si>
+    <t>Reviewed</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>some slides ignored</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1448,12 +1460,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1788,15 +1799,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="67.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1806,166 +1817,181 @@
       <c r="C1" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="D1" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="D2" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1973,10 +1999,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1984,10 +2010,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1995,10 +2021,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2006,10 +2032,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2017,10 +2043,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2028,10 +2054,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2039,10 +2065,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2050,10 +2076,10 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2061,10 +2087,10 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2072,10 +2098,10 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2083,10 +2109,10 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2094,10 +2120,10 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" t="s">
         <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2105,10 +2131,10 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2116,10 +2142,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2127,10 +2153,10 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2138,10 +2164,10 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2149,10 +2175,10 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2160,10 +2186,10 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2171,10 +2197,10 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" t="s">
         <v>71</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2182,10 +2208,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" t="s">
         <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2193,10 +2219,10 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2204,10 +2230,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+      <c r="A38" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2215,10 +2241,10 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2226,10 +2252,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+      <c r="A40" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" t="s">
         <v>81</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2237,10 +2263,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2248,10 +2274,10 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="A42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2259,10 +2285,10 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2270,10 +2296,10 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+      <c r="A44" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2281,10 +2307,10 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
+      <c r="A45" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" t="s">
         <v>91</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -2292,10 +2318,10 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" t="s">
         <v>93</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2303,10 +2329,10 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -2314,186 +2340,192 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+      <c r="A48" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" t="s">
         <v>99</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" t="s">
         <v>101</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" t="s">
         <v>103</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" t="s">
         <v>107</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" t="s">
         <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" t="s">
         <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" t="s">
         <v>117</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" t="s">
         <v>119</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" t="s">
         <v>123</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+      <c r="D61" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" t="s">
         <v>125</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" t="s">
         <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -2501,10 +2533,10 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
+      <c r="A65" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -2512,10 +2544,10 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
+      <c r="A66" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" t="s">
         <v>133</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -2523,10 +2555,10 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
+      <c r="A67" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" t="s">
         <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -2534,10 +2566,10 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
+      <c r="A68" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" t="s">
         <v>137</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -2545,10 +2577,10 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
+      <c r="A69" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" t="s">
         <v>139</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -2556,10 +2588,10 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
+      <c r="A70" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" t="s">
         <v>141</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -2567,10 +2599,10 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
+      <c r="A71" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" t="s">
         <v>143</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -2578,10 +2610,10 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
+      <c r="A72" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" t="s">
         <v>145</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -2589,10 +2621,10 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
+      <c r="A73" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" t="s">
         <v>147</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -2600,10 +2632,10 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
+      <c r="A74" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" t="s">
         <v>149</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -2611,10 +2643,10 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="4" t="s">
+      <c r="A75" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" t="s">
         <v>151</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -2622,10 +2654,10 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="4" t="s">
+      <c r="A76" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" t="s">
         <v>153</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -2633,10 +2665,10 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
+      <c r="A77" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" t="s">
         <v>155</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -2644,10 +2676,10 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
+      <c r="A78" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -2655,10 +2687,10 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
+      <c r="A79" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -2666,714 +2698,762 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
+      <c r="A80" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" t="s">
         <v>161</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" t="s">
         <v>163</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
+      <c r="D81" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" t="s">
         <v>165</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
+      <c r="D82" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" t="s">
         <v>167</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" t="s">
         <v>169</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" t="s">
         <v>171</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" t="s">
         <v>173</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="4" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" t="s">
         <v>175</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" t="s">
         <v>177</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="4" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" t="s">
         <v>179</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" t="s">
         <v>181</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="4" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" t="s">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" t="s">
         <v>185</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" t="s">
         <v>187</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" t="s">
         <v>189</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" t="s">
         <v>191</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="4" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" t="s">
         <v>193</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" t="s">
         <v>195</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A98" s="4" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" t="s">
         <v>197</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" t="s">
         <v>199</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="4" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" t="s">
         <v>201</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" s="4" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" t="s">
         <v>203</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="4" t="s">
+      <c r="D101" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" t="s">
         <v>205</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
+      <c r="D102" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" t="s">
         <v>207</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" t="s">
         <v>209</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" t="s">
         <v>211</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" t="s">
         <v>213</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" t="s">
         <v>215</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" t="s">
         <v>217</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109" s="4" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" t="s">
         <v>219</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A110" s="4" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" t="s">
         <v>221</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" s="4" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" t="s">
         <v>223</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" t="s">
         <v>225</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" t="s">
         <v>227</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" t="s">
         <v>229</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A115" s="4" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" t="s">
         <v>231</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A116" s="4" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" t="s">
         <v>233</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A117" s="4" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" t="s">
         <v>235</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A118" s="4" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
         <v>236</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" t="s">
         <v>237</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A119" s="4" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
         <v>238</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" t="s">
         <v>239</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
         <v>240</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" t="s">
         <v>241</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A121" s="4" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>242</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" t="s">
         <v>243</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A122" s="4" t="s">
+      <c r="D121" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
         <v>244</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" t="s">
         <v>245</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A123" s="4" t="s">
+      <c r="D122" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
         <v>246</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" t="s">
         <v>247</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A124" s="4" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
         <v>248</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" t="s">
         <v>249</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A125" s="4" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
         <v>250</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" t="s">
         <v>251</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A126" s="4" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
         <v>252</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" t="s">
         <v>253</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A127" s="4" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
         <v>254</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" t="s">
         <v>255</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A128" s="4" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
         <v>256</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" t="s">
         <v>257</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A129" s="4" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>258</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" t="s">
         <v>259</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A130" s="4" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
         <v>260</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" t="s">
         <v>261</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A131" s="4" t="s">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
         <v>262</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" t="s">
         <v>263</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A132" s="4" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
         <v>264</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" t="s">
         <v>265</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A133" s="4" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
         <v>266</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" t="s">
         <v>267</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A134" s="4" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
         <v>268</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" t="s">
         <v>269</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A135" s="4" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
         <v>270</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" t="s">
         <v>271</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A136" s="4" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
         <v>272</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" t="s">
         <v>273</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A137" s="4" t="s">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
         <v>274</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" t="s">
         <v>275</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A138" s="4" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
         <v>276</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" t="s">
         <v>277</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A139" s="4" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
         <v>278</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" t="s">
         <v>279</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A140" s="4" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>280</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" t="s">
         <v>281</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A141" s="4" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
         <v>282</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" t="s">
         <v>283</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A142" s="4" t="s">
+      <c r="D141" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>284</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" t="s">
         <v>285</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A143" s="4" t="s">
+      <c r="D142" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
         <v>286</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" t="s">
         <v>287</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
         <v>288</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" t="s">
         <v>289</v>
       </c>
       <c r="C144" s="2" t="s">
@@ -3381,10 +3461,10 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A145" s="4" t="s">
+      <c r="A145" t="s">
         <v>290</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" t="s">
         <v>291</v>
       </c>
       <c r="C145" s="2" t="s">
@@ -3392,10 +3472,10 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A146" s="4" t="s">
+      <c r="A146" t="s">
         <v>292</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" t="s">
         <v>293</v>
       </c>
       <c r="C146" s="2" t="s">
@@ -3403,10 +3483,10 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A147" s="4" t="s">
+      <c r="A147" t="s">
         <v>294</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" t="s">
         <v>295</v>
       </c>
       <c r="C147" s="2" t="s">
@@ -3414,10 +3494,10 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A148" s="4" t="s">
+      <c r="A148" t="s">
         <v>296</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" t="s">
         <v>297</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -3425,10 +3505,10 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A149" s="4" t="s">
+      <c r="A149" t="s">
         <v>298</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" t="s">
         <v>299</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -3436,10 +3516,10 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A150" s="4" t="s">
+      <c r="A150" t="s">
         <v>300</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" t="s">
         <v>301</v>
       </c>
       <c r="C150" s="2" t="s">
@@ -3447,10 +3527,10 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A151" s="4" t="s">
+      <c r="A151" t="s">
         <v>302</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" t="s">
         <v>303</v>
       </c>
       <c r="C151" s="2" t="s">
@@ -3458,10 +3538,10 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A152" s="4" t="s">
+      <c r="A152" t="s">
         <v>304</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" t="s">
         <v>305</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -3469,10 +3549,10 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A153" s="4" t="s">
+      <c r="A153" t="s">
         <v>306</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" t="s">
         <v>307</v>
       </c>
       <c r="C153" s="2" t="s">
@@ -3480,10 +3560,10 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A154" s="4" t="s">
+      <c r="A154" t="s">
         <v>308</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" t="s">
         <v>309</v>
       </c>
       <c r="C154" s="2" t="s">
@@ -3491,10 +3571,10 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A155" s="4" t="s">
+      <c r="A155" t="s">
         <v>310</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" t="s">
         <v>311</v>
       </c>
       <c r="C155" s="2" t="s">
@@ -3502,10 +3582,10 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A156" s="4" t="s">
+      <c r="A156" t="s">
         <v>312</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" t="s">
         <v>313</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -3513,10 +3593,10 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A157" s="4" t="s">
+      <c r="A157" t="s">
         <v>314</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" t="s">
         <v>315</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -3524,10 +3604,10 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A158" s="4" t="s">
+      <c r="A158" t="s">
         <v>316</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" t="s">
         <v>317</v>
       </c>
       <c r="C158" s="2" t="s">
@@ -3535,10 +3615,10 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A159" s="4" t="s">
+      <c r="A159" t="s">
         <v>318</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" t="s">
         <v>319</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -3546,538 +3626,574 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A160" s="4" t="s">
+      <c r="A160" t="s">
         <v>320</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" t="s">
         <v>321</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A161" s="4" t="s">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>322</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" t="s">
         <v>323</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A162" s="4" t="s">
+      <c r="D161" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>324</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" t="s">
         <v>325</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A163" s="4" t="s">
+      <c r="D162" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>326</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" t="s">
         <v>327</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A164" s="4" t="s">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>328</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" t="s">
         <v>329</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A165" s="4" t="s">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
         <v>330</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" t="s">
         <v>331</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A166" s="4" t="s">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
         <v>332</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" t="s">
         <v>333</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A167" s="4" t="s">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
         <v>334</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" t="s">
         <v>335</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A168" s="4" t="s">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
         <v>336</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" t="s">
         <v>337</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A169" s="4" t="s">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
         <v>338</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" t="s">
         <v>339</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A170" s="4" t="s">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
         <v>340</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" t="s">
         <v>341</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A171" s="4" t="s">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
         <v>342</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" t="s">
         <v>343</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A172" s="4" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
         <v>344</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" t="s">
         <v>345</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A173" s="4" t="s">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
         <v>346</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" t="s">
         <v>347</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A174" s="4" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
         <v>348</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" t="s">
         <v>349</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A175" s="4" t="s">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
         <v>350</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" t="s">
         <v>351</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A176" s="4" t="s">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
         <v>352</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" t="s">
         <v>353</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A177" s="4" t="s">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
         <v>354</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" t="s">
         <v>355</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A178" s="4" t="s">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
         <v>356</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" t="s">
         <v>357</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A179" s="4" t="s">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
         <v>358</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" t="s">
         <v>359</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180" s="4" t="s">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
         <v>360</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" t="s">
         <v>361</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A181" s="4" t="s">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
         <v>362</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" t="s">
         <v>363</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A182" s="4" t="s">
+      <c r="D181" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
         <v>364</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" t="s">
         <v>365</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A183" s="4" t="s">
+      <c r="D182" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
         <v>366</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" t="s">
         <v>367</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A184" s="4" t="s">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
         <v>368</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" t="s">
         <v>369</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" s="4" t="s">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>370</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" t="s">
         <v>371</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186" s="4" t="s">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>372</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" t="s">
         <v>373</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A187" s="4" t="s">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
         <v>374</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" t="s">
         <v>375</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A188" s="4" t="s">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
         <v>376</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" t="s">
         <v>377</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A189" s="4" t="s">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
         <v>378</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" t="s">
         <v>379</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A190" s="4" t="s">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
         <v>380</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" t="s">
         <v>381</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A191" s="4" t="s">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
         <v>382</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" t="s">
         <v>383</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A192" s="4" t="s">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
         <v>384</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" t="s">
         <v>385</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A193" s="4" t="s">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" t="s">
         <v>387</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A194" s="4" t="s">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
         <v>388</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" t="s">
         <v>389</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A195" s="4" t="s">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
         <v>390</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" t="s">
         <v>391</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A196" s="4" t="s">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
         <v>392</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" t="s">
         <v>393</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A197" s="4" t="s">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
         <v>394</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" t="s">
         <v>395</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A198" s="4" t="s">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
         <v>396</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" t="s">
         <v>397</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A199" s="4" t="s">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>398</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" t="s">
         <v>399</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A200" s="4" t="s">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
         <v>400</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" t="s">
         <v>401</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A201" s="4" t="s">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
         <v>402</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" t="s">
         <v>403</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A202" s="4" t="s">
+      <c r="D201" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
         <v>404</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" t="s">
         <v>405</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A203" s="4" t="s">
+      <c r="D202" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
         <v>406</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" t="s">
         <v>407</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A204" s="4" t="s">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
         <v>408</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" t="s">
         <v>409</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A205" s="4" t="s">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
         <v>410</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" t="s">
         <v>411</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A206" s="4" t="s">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
         <v>412</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" t="s">
         <v>413</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A207" s="4" t="s">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
         <v>414</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" t="s">
         <v>415</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A208" s="4" t="s">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
         <v>416</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" t="s">
         <v>417</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -4085,10 +4201,10 @@
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A209" s="4" t="s">
+      <c r="A209" t="s">
         <v>418</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" t="s">
         <v>419</v>
       </c>
       <c r="C209" s="2" t="s">
@@ -4096,10 +4212,10 @@
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A210" s="4" t="s">
+      <c r="A210" t="s">
         <v>420</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" t="s">
         <v>421</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -4107,10 +4223,10 @@
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A211" s="4" t="s">
+      <c r="A211" t="s">
         <v>422</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" t="s">
         <v>423</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -4118,10 +4234,10 @@
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A212" s="4" t="s">
+      <c r="A212" t="s">
         <v>424</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" t="s">
         <v>425</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -4129,10 +4245,10 @@
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A213" s="4" t="s">
+      <c r="A213" t="s">
         <v>426</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" t="s">
         <v>427</v>
       </c>
       <c r="C213" s="2" t="s">
@@ -4140,10 +4256,10 @@
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A214" s="4" t="s">
+      <c r="A214" t="s">
         <v>428</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" t="s">
         <v>429</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -4151,10 +4267,10 @@
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A215" s="4" t="s">
+      <c r="A215" t="s">
         <v>430</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" t="s">
         <v>431</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -4162,10 +4278,10 @@
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A216" s="4" t="s">
+      <c r="A216" t="s">
         <v>432</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" t="s">
         <v>433</v>
       </c>
       <c r="C216" s="2" t="s">
@@ -4173,10 +4289,10 @@
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A217" s="4" t="s">
+      <c r="A217" t="s">
         <v>434</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" t="s">
         <v>435</v>
       </c>
       <c r="C217" s="2" t="s">
@@ -4184,10 +4300,10 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A218" s="4" t="s">
+      <c r="A218" t="s">
         <v>436</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" t="s">
         <v>437</v>
       </c>
       <c r="C218" s="2" t="s">
@@ -4195,10 +4311,10 @@
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A219" s="4" t="s">
+      <c r="A219" t="s">
         <v>438</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" t="s">
         <v>439</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -4206,10 +4322,10 @@
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A220" s="4" t="s">
+      <c r="A220" t="s">
         <v>440</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" t="s">
         <v>441</v>
       </c>
       <c r="C220" s="2" t="s">

--- a/code/data/coursedata.xlsx
+++ b/code/data/coursedata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MyAccount/Documents/_Development/generateCorporateCoursedata/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA866E8B-5AD5-CA47-B2AC-C139CEF52FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E22CC9-D07B-9147-A217-1DF1DAF81265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17060" yWindow="-21000" windowWidth="29840" windowHeight="21000" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
+    <workbookView xWindow="25980" yWindow="-19620" windowWidth="28700" windowHeight="18140" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="456">
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="452">
   <si>
     <t>Over-Reliance on AI (Automation Bias)</t>
   </si>
@@ -161,9 +155,6 @@
     <t>Corporate</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>AI in Safety-Critical Environments: What Can Go Wrong?</t>
   </si>
   <si>
@@ -1392,9 +1383,6 @@
   </si>
   <si>
     <t>Education &amp; Public Sector: Education, Government Services, Non-Profit organizations </t>
-  </si>
-  <si>
-    <t>Reviewed</t>
   </si>
   <si>
     <t>Yes</t>
@@ -1410,7 +1398,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1429,14 +1417,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1460,11 +1440,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
@@ -1808,17 +1787,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>41</v>
+      <c r="C1" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1829,10 +1811,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>453</v>
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1843,13 +1828,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>454</v>
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1860,10 +1845,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>453</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1874,7 +1856,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1885,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1896,7 +1878,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1907,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1918,7 +1900,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1929,7 +1911,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1940,7 +1922,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1951,7 +1933,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1962,7 +1944,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1973,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1984,7 +1966,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1995,10 +1977,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2006,10 +1988,10 @@
         <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2017,10 +1999,10 @@
         <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2028,2311 +2010,2331 @@
         <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>58</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>64</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>66</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>68</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>76</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>80</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>82</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>88</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>90</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>92</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>94</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>96</v>
       </c>
-      <c r="B48" t="s">
-        <v>97</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
         <v>98</v>
       </c>
-      <c r="B49" t="s">
-        <v>99</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
         <v>100</v>
       </c>
-      <c r="B50" t="s">
-        <v>101</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" t="s">
         <v>102</v>
       </c>
-      <c r="B51" t="s">
-        <v>103</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" t="s">
         <v>104</v>
       </c>
-      <c r="B52" t="s">
-        <v>105</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="B53" t="s">
-        <v>107</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" t="s">
         <v>108</v>
       </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
         <v>110</v>
       </c>
-      <c r="B55" t="s">
-        <v>111</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
         <v>112</v>
       </c>
-      <c r="B56" t="s">
-        <v>113</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
         <v>114</v>
       </c>
-      <c r="B57" t="s">
-        <v>115</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
         <v>116</v>
       </c>
-      <c r="B58" t="s">
-        <v>117</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" t="s">
         <v>118</v>
       </c>
-      <c r="B59" t="s">
-        <v>119</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
         <v>120</v>
       </c>
-      <c r="B60" t="s">
-        <v>121</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" t="s">
         <v>122</v>
       </c>
-      <c r="B61" t="s">
-        <v>123</v>
-      </c>
       <c r="C61" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" t="s">
         <v>124</v>
       </c>
-      <c r="B62" t="s">
-        <v>125</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" t="s">
         <v>126</v>
       </c>
-      <c r="B63" t="s">
-        <v>127</v>
-      </c>
       <c r="C63" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" t="s">
         <v>128</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>130</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>131</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>132</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>134</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>135</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>136</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>138</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>140</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>142</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>144</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>146</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>148</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>150</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>152</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>154</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>156</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>158</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>160</v>
       </c>
-      <c r="B80" t="s">
-        <v>161</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" t="s">
         <v>162</v>
       </c>
-      <c r="B81" t="s">
-        <v>163</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" t="s">
         <v>164</v>
       </c>
-      <c r="B82" t="s">
-        <v>165</v>
-      </c>
       <c r="C82" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" t="s">
         <v>166</v>
       </c>
-      <c r="B83" t="s">
-        <v>167</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" t="s">
         <v>168</v>
       </c>
-      <c r="B84" t="s">
-        <v>169</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" t="s">
         <v>170</v>
       </c>
-      <c r="B85" t="s">
-        <v>171</v>
-      </c>
       <c r="C85" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" t="s">
         <v>172</v>
       </c>
-      <c r="B86" t="s">
-        <v>173</v>
-      </c>
       <c r="C86" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" t="s">
         <v>174</v>
       </c>
-      <c r="B87" t="s">
-        <v>175</v>
-      </c>
       <c r="C87" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" t="s">
         <v>176</v>
       </c>
-      <c r="B88" t="s">
-        <v>177</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" t="s">
         <v>178</v>
       </c>
-      <c r="B89" t="s">
-        <v>179</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" t="s">
         <v>180</v>
       </c>
-      <c r="B90" t="s">
-        <v>181</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" t="s">
         <v>182</v>
       </c>
-      <c r="B91" t="s">
-        <v>183</v>
-      </c>
       <c r="C91" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" t="s">
         <v>184</v>
       </c>
-      <c r="B92" t="s">
-        <v>185</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" t="s">
         <v>186</v>
       </c>
-      <c r="B93" t="s">
-        <v>187</v>
-      </c>
       <c r="C93" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" t="s">
         <v>188</v>
       </c>
-      <c r="B94" t="s">
-        <v>189</v>
-      </c>
       <c r="C94" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" t="s">
         <v>190</v>
       </c>
-      <c r="B95" t="s">
-        <v>191</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>191</v>
+      </c>
+      <c r="B96" t="s">
         <v>192</v>
       </c>
-      <c r="B96" t="s">
-        <v>193</v>
-      </c>
       <c r="C96" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>193</v>
+      </c>
+      <c r="B97" t="s">
         <v>194</v>
       </c>
-      <c r="B97" t="s">
-        <v>195</v>
-      </c>
       <c r="C97" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>195</v>
+      </c>
+      <c r="B98" t="s">
         <v>196</v>
       </c>
-      <c r="B98" t="s">
-        <v>197</v>
-      </c>
       <c r="C98" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99" t="s">
         <v>198</v>
       </c>
-      <c r="B99" t="s">
-        <v>199</v>
-      </c>
       <c r="C99" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>199</v>
+      </c>
+      <c r="B100" t="s">
         <v>200</v>
       </c>
-      <c r="B100" t="s">
-        <v>201</v>
-      </c>
       <c r="C100" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" t="s">
         <v>202</v>
       </c>
-      <c r="B101" t="s">
-        <v>203</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>203</v>
+      </c>
+      <c r="B102" t="s">
         <v>204</v>
       </c>
-      <c r="B102" t="s">
-        <v>205</v>
-      </c>
       <c r="C102" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>205</v>
+      </c>
+      <c r="B103" t="s">
         <v>206</v>
       </c>
-      <c r="B103" t="s">
-        <v>207</v>
-      </c>
       <c r="C103" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" t="s">
         <v>208</v>
       </c>
-      <c r="B104" t="s">
-        <v>209</v>
-      </c>
       <c r="C104" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>209</v>
+      </c>
+      <c r="B105" t="s">
         <v>210</v>
       </c>
-      <c r="B105" t="s">
-        <v>211</v>
-      </c>
       <c r="C105" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" t="s">
         <v>212</v>
       </c>
-      <c r="B106" t="s">
-        <v>213</v>
-      </c>
       <c r="C106" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>213</v>
+      </c>
+      <c r="B107" t="s">
         <v>214</v>
       </c>
-      <c r="B107" t="s">
-        <v>215</v>
-      </c>
       <c r="C107" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>215</v>
+      </c>
+      <c r="B108" t="s">
         <v>216</v>
       </c>
-      <c r="B108" t="s">
-        <v>217</v>
-      </c>
       <c r="C108" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>217</v>
+      </c>
+      <c r="B109" t="s">
         <v>218</v>
       </c>
-      <c r="B109" t="s">
-        <v>219</v>
-      </c>
       <c r="C109" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>219</v>
+      </c>
+      <c r="B110" t="s">
         <v>220</v>
       </c>
-      <c r="B110" t="s">
-        <v>221</v>
-      </c>
       <c r="C110" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>221</v>
+      </c>
+      <c r="B111" t="s">
         <v>222</v>
       </c>
-      <c r="B111" t="s">
-        <v>223</v>
-      </c>
       <c r="C111" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>223</v>
+      </c>
+      <c r="B112" t="s">
         <v>224</v>
       </c>
-      <c r="B112" t="s">
-        <v>225</v>
-      </c>
       <c r="C112" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>225</v>
+      </c>
+      <c r="B113" t="s">
         <v>226</v>
       </c>
-      <c r="B113" t="s">
-        <v>227</v>
-      </c>
       <c r="C113" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>227</v>
+      </c>
+      <c r="B114" t="s">
         <v>228</v>
       </c>
-      <c r="B114" t="s">
-        <v>229</v>
-      </c>
       <c r="C114" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>229</v>
+      </c>
+      <c r="B115" t="s">
         <v>230</v>
       </c>
-      <c r="B115" t="s">
-        <v>231</v>
-      </c>
       <c r="C115" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>231</v>
+      </c>
+      <c r="B116" t="s">
         <v>232</v>
       </c>
-      <c r="B116" t="s">
-        <v>233</v>
-      </c>
       <c r="C116" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>233</v>
+      </c>
+      <c r="B117" t="s">
         <v>234</v>
       </c>
-      <c r="B117" t="s">
-        <v>235</v>
-      </c>
       <c r="C117" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>235</v>
+      </c>
+      <c r="B118" t="s">
         <v>236</v>
       </c>
-      <c r="B118" t="s">
-        <v>237</v>
-      </c>
       <c r="C118" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>237</v>
+      </c>
+      <c r="B119" t="s">
         <v>238</v>
       </c>
-      <c r="B119" t="s">
-        <v>239</v>
-      </c>
       <c r="C119" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>239</v>
+      </c>
+      <c r="B120" t="s">
         <v>240</v>
       </c>
-      <c r="B120" t="s">
-        <v>241</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>241</v>
+      </c>
+      <c r="B121" t="s">
         <v>242</v>
       </c>
-      <c r="B121" t="s">
-        <v>243</v>
-      </c>
       <c r="C121" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>243</v>
+      </c>
+      <c r="B122" t="s">
         <v>244</v>
       </c>
-      <c r="B122" t="s">
-        <v>245</v>
-      </c>
       <c r="C122" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123" t="s">
         <v>246</v>
       </c>
-      <c r="B123" t="s">
-        <v>247</v>
-      </c>
       <c r="C123" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>247</v>
+      </c>
+      <c r="B124" t="s">
         <v>248</v>
       </c>
-      <c r="B124" t="s">
-        <v>249</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>249</v>
+      </c>
+      <c r="B125" t="s">
         <v>250</v>
       </c>
-      <c r="B125" t="s">
-        <v>251</v>
-      </c>
       <c r="C125" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>251</v>
+      </c>
+      <c r="B126" t="s">
         <v>252</v>
       </c>
-      <c r="B126" t="s">
-        <v>253</v>
-      </c>
       <c r="C126" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>253</v>
+      </c>
+      <c r="B127" t="s">
         <v>254</v>
       </c>
-      <c r="B127" t="s">
-        <v>255</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>255</v>
+      </c>
+      <c r="B128" t="s">
         <v>256</v>
       </c>
-      <c r="B128" t="s">
-        <v>257</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" t="s">
         <v>258</v>
       </c>
-      <c r="B129" t="s">
-        <v>259</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>259</v>
+      </c>
+      <c r="B130" t="s">
         <v>260</v>
       </c>
-      <c r="B130" t="s">
-        <v>261</v>
-      </c>
       <c r="C130" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" t="s">
         <v>262</v>
       </c>
-      <c r="B131" t="s">
-        <v>263</v>
-      </c>
       <c r="C131" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>263</v>
+      </c>
+      <c r="B132" t="s">
         <v>264</v>
       </c>
-      <c r="B132" t="s">
-        <v>265</v>
-      </c>
       <c r="C132" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>265</v>
+      </c>
+      <c r="B133" t="s">
         <v>266</v>
       </c>
-      <c r="B133" t="s">
-        <v>267</v>
-      </c>
       <c r="C133" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>267</v>
+      </c>
+      <c r="B134" t="s">
         <v>268</v>
       </c>
-      <c r="B134" t="s">
-        <v>269</v>
-      </c>
       <c r="C134" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>269</v>
+      </c>
+      <c r="B135" t="s">
         <v>270</v>
       </c>
-      <c r="B135" t="s">
-        <v>271</v>
-      </c>
       <c r="C135" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>271</v>
+      </c>
+      <c r="B136" t="s">
         <v>272</v>
       </c>
-      <c r="B136" t="s">
-        <v>273</v>
-      </c>
       <c r="C136" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>273</v>
+      </c>
+      <c r="B137" t="s">
         <v>274</v>
       </c>
-      <c r="B137" t="s">
-        <v>275</v>
-      </c>
       <c r="C137" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>275</v>
+      </c>
+      <c r="B138" t="s">
         <v>276</v>
       </c>
-      <c r="B138" t="s">
-        <v>277</v>
-      </c>
       <c r="C138" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>277</v>
+      </c>
+      <c r="B139" t="s">
         <v>278</v>
       </c>
-      <c r="B139" t="s">
-        <v>279</v>
-      </c>
       <c r="C139" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>279</v>
+      </c>
+      <c r="B140" t="s">
         <v>280</v>
       </c>
-      <c r="B140" t="s">
-        <v>281</v>
-      </c>
       <c r="C140" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
+        <v>281</v>
+      </c>
+      <c r="B141" t="s">
         <v>282</v>
       </c>
-      <c r="B141" t="s">
-        <v>283</v>
-      </c>
       <c r="C141" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>283</v>
+      </c>
+      <c r="B142" t="s">
         <v>284</v>
       </c>
-      <c r="B142" t="s">
-        <v>285</v>
-      </c>
       <c r="C142" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>285</v>
+      </c>
+      <c r="B143" t="s">
         <v>286</v>
       </c>
-      <c r="B143" t="s">
-        <v>287</v>
-      </c>
       <c r="C143" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>287</v>
+      </c>
+      <c r="B144" t="s">
         <v>288</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>289</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>290</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
         <v>291</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
         <v>292</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
         <v>293</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
         <v>294</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
         <v>295</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>296</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
         <v>297</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
         <v>298</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
         <v>299</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
         <v>300</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
         <v>301</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
         <v>302</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
         <v>303</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
         <v>304</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
         <v>305</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
         <v>306</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
         <v>307</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
         <v>308</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
         <v>309</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
         <v>310</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
         <v>311</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>312</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>313</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>314</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
         <v>315</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
         <v>316</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>317</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>318</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>319</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>320</v>
       </c>
-      <c r="B160" t="s">
-        <v>321</v>
-      </c>
       <c r="C160" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>321</v>
+      </c>
+      <c r="B161" t="s">
         <v>322</v>
       </c>
-      <c r="B161" t="s">
-        <v>323</v>
-      </c>
       <c r="C161" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>455</v>
+        <v>446</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>451</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>323</v>
+      </c>
+      <c r="B162" t="s">
         <v>324</v>
       </c>
-      <c r="B162" t="s">
-        <v>325</v>
-      </c>
       <c r="C162" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
+        <v>325</v>
+      </c>
+      <c r="B163" t="s">
         <v>326</v>
       </c>
-      <c r="B163" t="s">
-        <v>327</v>
-      </c>
       <c r="C163" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>327</v>
+      </c>
+      <c r="B164" t="s">
         <v>328</v>
       </c>
-      <c r="B164" t="s">
-        <v>329</v>
-      </c>
       <c r="C164" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>329</v>
+      </c>
+      <c r="B165" t="s">
         <v>330</v>
       </c>
-      <c r="B165" t="s">
-        <v>331</v>
-      </c>
       <c r="C165" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>331</v>
+      </c>
+      <c r="B166" t="s">
         <v>332</v>
       </c>
-      <c r="B166" t="s">
-        <v>333</v>
-      </c>
       <c r="C166" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>333</v>
+      </c>
+      <c r="B167" t="s">
         <v>334</v>
       </c>
-      <c r="B167" t="s">
-        <v>335</v>
-      </c>
       <c r="C167" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>335</v>
+      </c>
+      <c r="B168" t="s">
         <v>336</v>
       </c>
-      <c r="B168" t="s">
-        <v>337</v>
-      </c>
       <c r="C168" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>337</v>
+      </c>
+      <c r="B169" t="s">
         <v>338</v>
       </c>
-      <c r="B169" t="s">
-        <v>339</v>
-      </c>
       <c r="C169" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>339</v>
+      </c>
+      <c r="B170" t="s">
         <v>340</v>
       </c>
-      <c r="B170" t="s">
-        <v>341</v>
-      </c>
       <c r="C170" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
+        <v>341</v>
+      </c>
+      <c r="B171" t="s">
         <v>342</v>
       </c>
-      <c r="B171" t="s">
-        <v>343</v>
-      </c>
       <c r="C171" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>343</v>
+      </c>
+      <c r="B172" t="s">
         <v>344</v>
       </c>
-      <c r="B172" t="s">
-        <v>345</v>
-      </c>
       <c r="C172" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
+        <v>345</v>
+      </c>
+      <c r="B173" t="s">
         <v>346</v>
       </c>
-      <c r="B173" t="s">
-        <v>347</v>
-      </c>
       <c r="C173" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>347</v>
+      </c>
+      <c r="B174" t="s">
         <v>348</v>
       </c>
-      <c r="B174" t="s">
-        <v>349</v>
-      </c>
       <c r="C174" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>349</v>
+      </c>
+      <c r="B175" t="s">
         <v>350</v>
       </c>
-      <c r="B175" t="s">
-        <v>351</v>
-      </c>
       <c r="C175" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>351</v>
+      </c>
+      <c r="B176" t="s">
         <v>352</v>
       </c>
-      <c r="B176" t="s">
-        <v>353</v>
-      </c>
       <c r="C176" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>353</v>
+      </c>
+      <c r="B177" t="s">
         <v>354</v>
       </c>
-      <c r="B177" t="s">
-        <v>355</v>
-      </c>
       <c r="C177" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B178" t="s">
         <v>356</v>
       </c>
-      <c r="B178" t="s">
-        <v>357</v>
-      </c>
       <c r="C178" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>357</v>
+      </c>
+      <c r="B179" t="s">
         <v>358</v>
       </c>
-      <c r="B179" t="s">
-        <v>359</v>
-      </c>
       <c r="C179" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>359</v>
+      </c>
+      <c r="B180" t="s">
         <v>360</v>
       </c>
-      <c r="B180" t="s">
-        <v>361</v>
-      </c>
       <c r="C180" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>361</v>
+      </c>
+      <c r="B181" t="s">
         <v>362</v>
       </c>
-      <c r="B181" t="s">
-        <v>363</v>
-      </c>
       <c r="C181" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" t="s">
         <v>364</v>
       </c>
-      <c r="B182" t="s">
-        <v>365</v>
-      </c>
       <c r="C182" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" t="s">
         <v>366</v>
       </c>
-      <c r="B183" t="s">
-        <v>367</v>
-      </c>
       <c r="C183" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>367</v>
+      </c>
+      <c r="B184" t="s">
         <v>368</v>
       </c>
-      <c r="B184" t="s">
-        <v>369</v>
-      </c>
       <c r="C184" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>369</v>
+      </c>
+      <c r="B185" t="s">
         <v>370</v>
       </c>
-      <c r="B185" t="s">
-        <v>371</v>
-      </c>
       <c r="C185" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>371</v>
+      </c>
+      <c r="B186" t="s">
         <v>372</v>
       </c>
-      <c r="B186" t="s">
-        <v>373</v>
-      </c>
       <c r="C186" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>373</v>
+      </c>
+      <c r="B187" t="s">
         <v>374</v>
       </c>
-      <c r="B187" t="s">
-        <v>375</v>
-      </c>
       <c r="C187" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>375</v>
+      </c>
+      <c r="B188" t="s">
         <v>376</v>
       </c>
-      <c r="B188" t="s">
-        <v>377</v>
-      </c>
       <c r="C188" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" t="s">
         <v>378</v>
       </c>
-      <c r="B189" t="s">
-        <v>379</v>
-      </c>
       <c r="C189" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>379</v>
+      </c>
+      <c r="B190" t="s">
         <v>380</v>
       </c>
-      <c r="B190" t="s">
-        <v>381</v>
-      </c>
       <c r="C190" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>381</v>
+      </c>
+      <c r="B191" t="s">
         <v>382</v>
       </c>
-      <c r="B191" t="s">
-        <v>383</v>
-      </c>
       <c r="C191" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>383</v>
+      </c>
+      <c r="B192" t="s">
         <v>384</v>
       </c>
-      <c r="B192" t="s">
-        <v>385</v>
-      </c>
       <c r="C192" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>385</v>
+      </c>
+      <c r="B193" t="s">
         <v>386</v>
       </c>
-      <c r="B193" t="s">
-        <v>387</v>
-      </c>
       <c r="C193" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" t="s">
         <v>388</v>
       </c>
-      <c r="B194" t="s">
-        <v>389</v>
-      </c>
       <c r="C194" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B195" t="s">
         <v>390</v>
       </c>
-      <c r="B195" t="s">
-        <v>391</v>
-      </c>
       <c r="C195" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>391</v>
+      </c>
+      <c r="B196" t="s">
         <v>392</v>
       </c>
-      <c r="B196" t="s">
-        <v>393</v>
-      </c>
       <c r="C196" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>393</v>
+      </c>
+      <c r="B197" t="s">
         <v>394</v>
       </c>
-      <c r="B197" t="s">
-        <v>395</v>
-      </c>
       <c r="C197" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>395</v>
+      </c>
+      <c r="B198" t="s">
         <v>396</v>
       </c>
-      <c r="B198" t="s">
-        <v>397</v>
-      </c>
       <c r="C198" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>397</v>
+      </c>
+      <c r="B199" t="s">
         <v>398</v>
       </c>
-      <c r="B199" t="s">
-        <v>399</v>
-      </c>
       <c r="C199" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>399</v>
+      </c>
+      <c r="B200" t="s">
         <v>400</v>
       </c>
-      <c r="B200" t="s">
-        <v>401</v>
-      </c>
       <c r="C200" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>401</v>
+      </c>
+      <c r="B201" t="s">
         <v>402</v>
       </c>
-      <c r="B201" t="s">
-        <v>403</v>
-      </c>
       <c r="C201" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>403</v>
+      </c>
+      <c r="B202" t="s">
         <v>404</v>
       </c>
-      <c r="B202" t="s">
-        <v>405</v>
-      </c>
       <c r="C202" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>405</v>
+      </c>
+      <c r="B203" t="s">
         <v>406</v>
       </c>
-      <c r="B203" t="s">
-        <v>407</v>
-      </c>
       <c r="C203" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>407</v>
+      </c>
+      <c r="B204" t="s">
         <v>408</v>
       </c>
-      <c r="B204" t="s">
-        <v>409</v>
-      </c>
       <c r="C204" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>409</v>
+      </c>
+      <c r="B205" t="s">
         <v>410</v>
       </c>
-      <c r="B205" t="s">
-        <v>411</v>
-      </c>
       <c r="C205" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>411</v>
+      </c>
+      <c r="B206" t="s">
         <v>412</v>
       </c>
-      <c r="B206" t="s">
-        <v>413</v>
-      </c>
       <c r="C206" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>413</v>
+      </c>
+      <c r="B207" t="s">
         <v>414</v>
       </c>
-      <c r="B207" t="s">
-        <v>415</v>
-      </c>
       <c r="C207" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>415</v>
+      </c>
+      <c r="B208" t="s">
         <v>416</v>
       </c>
-      <c r="B208" t="s">
-        <v>417</v>
-      </c>
       <c r="C208" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>417</v>
+      </c>
+      <c r="B209" t="s">
         <v>418</v>
       </c>
-      <c r="B209" t="s">
-        <v>419</v>
-      </c>
       <c r="C209" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>419</v>
+      </c>
+      <c r="B210" t="s">
         <v>420</v>
       </c>
-      <c r="B210" t="s">
-        <v>421</v>
-      </c>
       <c r="C210" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>421</v>
+      </c>
+      <c r="B211" t="s">
         <v>422</v>
       </c>
-      <c r="B211" t="s">
-        <v>423</v>
-      </c>
       <c r="C211" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>423</v>
+      </c>
+      <c r="B212" t="s">
         <v>424</v>
       </c>
-      <c r="B212" t="s">
-        <v>425</v>
-      </c>
       <c r="C212" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>425</v>
+      </c>
+      <c r="B213" t="s">
         <v>426</v>
       </c>
-      <c r="B213" t="s">
-        <v>427</v>
-      </c>
       <c r="C213" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>427</v>
+      </c>
+      <c r="B214" t="s">
         <v>428</v>
       </c>
-      <c r="B214" t="s">
-        <v>429</v>
-      </c>
       <c r="C214" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>429</v>
+      </c>
+      <c r="B215" t="s">
         <v>430</v>
       </c>
-      <c r="B215" t="s">
-        <v>431</v>
-      </c>
       <c r="C215" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>431</v>
+      </c>
+      <c r="B216" t="s">
         <v>432</v>
       </c>
-      <c r="B216" t="s">
-        <v>433</v>
-      </c>
       <c r="C216" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>433</v>
+      </c>
+      <c r="B217" t="s">
         <v>434</v>
       </c>
-      <c r="B217" t="s">
-        <v>435</v>
-      </c>
       <c r="C217" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>435</v>
+      </c>
+      <c r="B218" t="s">
         <v>436</v>
       </c>
-      <c r="B218" t="s">
-        <v>437</v>
-      </c>
       <c r="C218" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>437</v>
+      </c>
+      <c r="B219" t="s">
         <v>438</v>
       </c>
-      <c r="B219" t="s">
-        <v>439</v>
-      </c>
       <c r="C219" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>440</v>
-      </c>
-      <c r="B220" t="s">
-        <v>441</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/code/data/coursedata.xlsx
+++ b/code/data/coursedata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MyAccount/Documents/_Development/generateCorporateCoursedata/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E22CC9-D07B-9147-A217-1DF1DAF81265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6485662-CB50-764F-B8A7-4558C7A53B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25980" yWindow="-19620" windowWidth="28700" windowHeight="18140" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
+    <workbookView xWindow="440" yWindow="1820" windowWidth="25520" windowHeight="17320" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="454">
   <si>
     <t>Over-Reliance on AI (Automation Bias)</t>
   </si>
@@ -1392,6 +1392,12 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>auto fixed</t>
+  </si>
+  <si>
+    <t>recorded</t>
   </si>
 </sst>
 </file>
@@ -1778,15 +1784,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="67.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="104.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1802,8 +1810,11 @@
       <c r="E1" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1819,8 +1830,11 @@
       <c r="E2" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1836,8 +1850,11 @@
       <c r="E3" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1847,8 +1864,11 @@
       <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1858,8 +1878,11 @@
       <c r="C5" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1869,8 +1892,11 @@
       <c r="C6" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1880,8 +1906,11 @@
       <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1891,8 +1920,11 @@
       <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1902,8 +1934,11 @@
       <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E9" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1913,8 +1948,11 @@
       <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E10" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1924,8 +1962,11 @@
       <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E11" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1935,8 +1976,11 @@
       <c r="C12" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E12" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1946,8 +1990,11 @@
       <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E13" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1957,8 +2004,11 @@
       <c r="C14" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E14" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1968,8 +2018,11 @@
       <c r="C15" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E15" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1979,8 +2032,11 @@
       <c r="C16" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1990,8 +2046,11 @@
       <c r="C17" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2001,8 +2060,11 @@
       <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2012,8 +2074,11 @@
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -2029,8 +2094,11 @@
       <c r="E20" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2046,8 +2114,11 @@
       <c r="E21" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2057,8 +2128,11 @@
       <c r="C22" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E22" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -2068,8 +2142,11 @@
       <c r="C23" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E23" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -2079,8 +2156,11 @@
       <c r="C24" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E24" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2090,8 +2170,11 @@
       <c r="C25" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -2101,8 +2184,11 @@
       <c r="C26" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E26" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -2112,8 +2198,11 @@
       <c r="C27" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E27" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -2123,8 +2212,11 @@
       <c r="C28" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E28" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -2134,8 +2226,11 @@
       <c r="C29" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E29" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -2145,8 +2240,11 @@
       <c r="C30" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E30" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2156,8 +2254,11 @@
       <c r="C31" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E31" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -2167,8 +2268,11 @@
       <c r="C32" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E32" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -2178,8 +2282,11 @@
       <c r="C33" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -2189,8 +2296,11 @@
       <c r="C34" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2200,8 +2310,11 @@
       <c r="C35" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -2211,8 +2324,11 @@
       <c r="C36" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E36" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -2222,8 +2338,11 @@
       <c r="C37" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E37" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -2233,8 +2352,11 @@
       <c r="C38" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E38" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -2244,8 +2366,11 @@
       <c r="C39" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E39" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -2261,8 +2386,11 @@
       <c r="E40" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2278,8 +2406,11 @@
       <c r="E41" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2289,8 +2420,11 @@
       <c r="C42" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E42" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2300,8 +2434,11 @@
       <c r="C43" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2311,8 +2448,11 @@
       <c r="C44" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E44" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2322,8 +2462,11 @@
       <c r="C45" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2333,8 +2476,11 @@
       <c r="C46" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E46" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2344,8 +2490,11 @@
       <c r="C47" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E47" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2355,8 +2504,11 @@
       <c r="C48" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E48" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2366,8 +2518,11 @@
       <c r="C49" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E49" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2377,8 +2532,11 @@
       <c r="C50" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E50" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2388,8 +2546,11 @@
       <c r="C51" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E51" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2399,8 +2560,11 @@
       <c r="C52" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E52" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2410,8 +2574,11 @@
       <c r="C53" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E53" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2421,8 +2588,11 @@
       <c r="C54" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E54" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2432,8 +2602,11 @@
       <c r="C55" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E55" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2443,8 +2616,11 @@
       <c r="C56" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E56" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2454,8 +2630,11 @@
       <c r="C57" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E57" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2465,8 +2644,11 @@
       <c r="C58" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E58" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2476,8 +2658,11 @@
       <c r="C59" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E59" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2493,8 +2678,11 @@
       <c r="E60" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2510,8 +2698,11 @@
       <c r="E61" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2521,8 +2712,11 @@
       <c r="C62" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E62" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2532,8 +2726,11 @@
       <c r="C63" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E63" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2543,8 +2740,11 @@
       <c r="C64" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E64" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2554,8 +2754,11 @@
       <c r="C65" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E65" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2565,8 +2768,11 @@
       <c r="C66" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E66" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2576,8 +2782,11 @@
       <c r="C67" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E67" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2587,8 +2796,11 @@
       <c r="C68" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E68" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2598,8 +2810,11 @@
       <c r="C69" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E69" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2609,8 +2824,11 @@
       <c r="C70" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E70" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2620,8 +2838,11 @@
       <c r="C71" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E71" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2631,8 +2852,11 @@
       <c r="C72" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E72" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2642,8 +2866,11 @@
       <c r="C73" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E73" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2653,8 +2880,11 @@
       <c r="C74" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E74" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2664,8 +2894,11 @@
       <c r="C75" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E75" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2675,8 +2908,11 @@
       <c r="C76" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E76" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2686,8 +2922,11 @@
       <c r="C77" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E77" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2697,8 +2936,11 @@
       <c r="C78" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E78" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2708,8 +2950,11 @@
       <c r="C79" s="2" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E79" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2724,6 +2969,9 @@
       </c>
       <c r="E80" s="1" t="s">
         <v>450</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -2753,6 +3001,9 @@
       <c r="C82" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E82" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
@@ -2764,6 +3015,9 @@
       <c r="C83" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E83" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
@@ -2775,6 +3029,9 @@
       <c r="C84" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E84" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
@@ -2786,6 +3043,9 @@
       <c r="C85" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E85" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
@@ -2797,6 +3057,9 @@
       <c r="C86" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E86" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
@@ -2808,6 +3071,9 @@
       <c r="C87" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E87" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
@@ -2819,6 +3085,9 @@
       <c r="C88" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E88" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
@@ -2830,6 +3099,9 @@
       <c r="C89" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E89" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
@@ -2841,6 +3113,9 @@
       <c r="C90" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E90" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
@@ -2852,6 +3127,9 @@
       <c r="C91" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E91" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
@@ -2863,6 +3141,9 @@
       <c r="C92" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E92" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
@@ -2874,6 +3155,9 @@
       <c r="C93" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E93" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
@@ -2885,6 +3169,9 @@
       <c r="C94" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E94" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
@@ -2896,6 +3183,9 @@
       <c r="C95" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E95" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
@@ -2907,6 +3197,9 @@
       <c r="C96" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E96" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
@@ -2918,6 +3211,9 @@
       <c r="C97" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E97" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
@@ -2929,6 +3225,9 @@
       <c r="C98" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E98" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
@@ -2940,6 +3239,9 @@
       <c r="C99" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E99" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
@@ -2985,6 +3287,9 @@
       <c r="C102" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E102" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
@@ -2996,6 +3301,9 @@
       <c r="C103" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E103" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
@@ -3007,6 +3315,9 @@
       <c r="C104" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E104" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
@@ -3018,6 +3329,9 @@
       <c r="C105" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E105" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
@@ -3029,6 +3343,9 @@
       <c r="C106" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E106" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
@@ -3040,6 +3357,9 @@
       <c r="C107" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E107" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
@@ -3051,6 +3371,9 @@
       <c r="C108" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E108" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
@@ -3062,6 +3385,9 @@
       <c r="C109" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E109" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
@@ -3073,6 +3399,9 @@
       <c r="C110" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E110" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
@@ -3084,6 +3413,9 @@
       <c r="C111" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E111" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
@@ -3095,6 +3427,9 @@
       <c r="C112" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E112" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
@@ -3106,6 +3441,9 @@
       <c r="C113" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E113" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
@@ -3117,6 +3455,9 @@
       <c r="C114" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E114" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
@@ -3128,6 +3469,9 @@
       <c r="C115" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E115" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
@@ -3139,6 +3483,9 @@
       <c r="C116" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E116" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
@@ -3150,6 +3497,9 @@
       <c r="C117" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E117" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
@@ -3161,6 +3511,9 @@
       <c r="C118" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E118" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
@@ -3172,6 +3525,9 @@
       <c r="C119" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="E119" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
@@ -3217,6 +3573,9 @@
       <c r="C122" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E122" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
@@ -3228,6 +3587,9 @@
       <c r="C123" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E123" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
@@ -3239,6 +3601,9 @@
       <c r="C124" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E124" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
@@ -3250,6 +3615,9 @@
       <c r="C125" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E125" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
@@ -3261,6 +3629,9 @@
       <c r="C126" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E126" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
@@ -3272,6 +3643,9 @@
       <c r="C127" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E127" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
@@ -3283,6 +3657,9 @@
       <c r="C128" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E128" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
@@ -3294,6 +3671,9 @@
       <c r="C129" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E129" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
@@ -3305,6 +3685,9 @@
       <c r="C130" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E130" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
@@ -3316,6 +3699,9 @@
       <c r="C131" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E131" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
@@ -3327,6 +3713,9 @@
       <c r="C132" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E132" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
@@ -3338,6 +3727,9 @@
       <c r="C133" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E133" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
@@ -3349,6 +3741,9 @@
       <c r="C134" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E134" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
@@ -3360,6 +3755,9 @@
       <c r="C135" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E135" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
@@ -3371,6 +3769,9 @@
       <c r="C136" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E136" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
@@ -3382,6 +3783,9 @@
       <c r="C137" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E137" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
@@ -3393,6 +3797,9 @@
       <c r="C138" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E138" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
@@ -3404,6 +3811,9 @@
       <c r="C139" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="E139" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
@@ -3449,6 +3859,9 @@
       <c r="C142" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E142" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
@@ -3460,6 +3873,9 @@
       <c r="C143" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E143" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
@@ -3471,6 +3887,9 @@
       <c r="C144" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E144" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
@@ -3482,6 +3901,9 @@
       <c r="C145" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E145" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
@@ -3493,6 +3915,9 @@
       <c r="C146" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E146" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
@@ -3504,6 +3929,9 @@
       <c r="C147" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E147" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
@@ -3515,6 +3943,9 @@
       <c r="C148" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E148" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
@@ -3526,6 +3957,9 @@
       <c r="C149" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E149" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
@@ -3537,6 +3971,9 @@
       <c r="C150" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E150" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
@@ -3548,6 +3985,9 @@
       <c r="C151" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E151" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
@@ -3559,6 +3999,9 @@
       <c r="C152" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E152" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
@@ -3570,6 +4013,9 @@
       <c r="C153" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E153" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
@@ -3581,6 +4027,9 @@
       <c r="C154" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E154" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
@@ -3592,6 +4041,9 @@
       <c r="C155" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E155" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
@@ -3603,6 +4055,9 @@
       <c r="C156" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E156" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
@@ -3614,6 +4069,9 @@
       <c r="C157" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E157" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
@@ -3625,6 +4083,9 @@
       <c r="C158" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E158" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
@@ -3636,6 +4097,9 @@
       <c r="C159" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="E159" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
@@ -3681,6 +4145,9 @@
       <c r="C162" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E162" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
@@ -3692,6 +4159,9 @@
       <c r="C163" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E163" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
@@ -3703,6 +4173,9 @@
       <c r="C164" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E164" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
@@ -3714,6 +4187,9 @@
       <c r="C165" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E165" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
@@ -3725,6 +4201,9 @@
       <c r="C166" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E166" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
@@ -3736,6 +4215,9 @@
       <c r="C167" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E167" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
@@ -3747,6 +4229,9 @@
       <c r="C168" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E168" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
@@ -3758,6 +4243,9 @@
       <c r="C169" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E169" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
@@ -3769,6 +4257,9 @@
       <c r="C170" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E170" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
@@ -3780,6 +4271,9 @@
       <c r="C171" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E171" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
@@ -3791,6 +4285,9 @@
       <c r="C172" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E172" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
@@ -3802,6 +4299,9 @@
       <c r="C173" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E173" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
@@ -3813,6 +4313,9 @@
       <c r="C174" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E174" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
@@ -3824,6 +4327,9 @@
       <c r="C175" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E175" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
@@ -3835,6 +4341,9 @@
       <c r="C176" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E176" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
@@ -3846,6 +4355,9 @@
       <c r="C177" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E177" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
@@ -3857,6 +4369,9 @@
       <c r="C178" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E178" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
@@ -3868,6 +4383,9 @@
       <c r="C179" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="E179" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
@@ -3913,6 +4431,9 @@
       <c r="C182" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E182" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
@@ -3924,6 +4445,9 @@
       <c r="C183" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E183" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
@@ -3935,6 +4459,9 @@
       <c r="C184" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E184" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
@@ -3946,6 +4473,9 @@
       <c r="C185" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E185" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
@@ -3957,6 +4487,9 @@
       <c r="C186" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E186" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
@@ -3968,6 +4501,9 @@
       <c r="C187" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E187" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
@@ -3979,6 +4515,9 @@
       <c r="C188" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E188" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
@@ -3990,6 +4529,9 @@
       <c r="C189" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E189" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
@@ -4001,6 +4543,9 @@
       <c r="C190" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E190" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
@@ -4012,6 +4557,9 @@
       <c r="C191" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E191" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
@@ -4023,6 +4571,9 @@
       <c r="C192" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E192" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
@@ -4034,6 +4585,9 @@
       <c r="C193" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E193" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
@@ -4045,6 +4599,9 @@
       <c r="C194" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E194" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
@@ -4056,6 +4613,9 @@
       <c r="C195" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E195" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
@@ -4067,6 +4627,9 @@
       <c r="C196" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E196" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
@@ -4078,6 +4641,9 @@
       <c r="C197" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E197" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
@@ -4089,6 +4655,9 @@
       <c r="C198" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E198" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
@@ -4100,6 +4669,9 @@
       <c r="C199" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="E199" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
@@ -4145,6 +4717,9 @@
       <c r="C202" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E202" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
@@ -4156,6 +4731,9 @@
       <c r="C203" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E203" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
@@ -4167,6 +4745,9 @@
       <c r="C204" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E204" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
@@ -4178,6 +4759,9 @@
       <c r="C205" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E205" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
@@ -4189,6 +4773,9 @@
       <c r="C206" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E206" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
@@ -4200,6 +4787,9 @@
       <c r="C207" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="E207" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
@@ -4211,8 +4801,11 @@
       <c r="C208" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E208" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>417</v>
       </c>
@@ -4222,8 +4815,11 @@
       <c r="C209" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E209" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>419</v>
       </c>
@@ -4233,8 +4829,11 @@
       <c r="C210" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E210" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>421</v>
       </c>
@@ -4244,8 +4843,11 @@
       <c r="C211" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E211" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>423</v>
       </c>
@@ -4255,8 +4857,11 @@
       <c r="C212" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E212" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>425</v>
       </c>
@@ -4266,8 +4871,11 @@
       <c r="C213" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E213" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>427</v>
       </c>
@@ -4277,8 +4885,11 @@
       <c r="C214" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E214" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>429</v>
       </c>
@@ -4288,8 +4899,11 @@
       <c r="C215" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E215" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>431</v>
       </c>
@@ -4299,8 +4913,11 @@
       <c r="C216" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E216" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>433</v>
       </c>
@@ -4310,8 +4927,11 @@
       <c r="C217" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E217" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>435</v>
       </c>
@@ -4321,8 +4941,11 @@
       <c r="C218" s="2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E218" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>437</v>
       </c>
@@ -4331,6 +4954,9 @@
       </c>
       <c r="C219" s="2" t="s">
         <v>448</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/coursedata.xlsx
+++ b/code/data/coursedata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MyAccount/Documents/_Development/generateCorporateCoursedata/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6485662-CB50-764F-B8A7-4558C7A53B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7C7341-6C55-964B-9093-6CCEBB376103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="440" yWindow="1820" windowWidth="25520" windowHeight="17320" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="457">
   <si>
     <t>Over-Reliance on AI (Automation Bias)</t>
   </si>
@@ -1398,13 +1398,22 @@
   </si>
   <si>
     <t>recorded</t>
+  </si>
+  <si>
+    <t>audio exported</t>
+  </si>
+  <si>
+    <t>Batch 1</t>
+  </si>
+  <si>
+    <t>Batch 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1423,6 +1432,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1784,17 +1799,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
-  <dimension ref="A1:F219"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="43.1640625" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1813,8 +1828,14 @@
       <c r="F1" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1833,8 +1854,14 @@
       <c r="F2" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1853,8 +1880,14 @@
       <c r="F3" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1867,8 +1900,17 @@
       <c r="E4" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1881,8 +1923,17 @@
       <c r="E5" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1895,8 +1946,17 @@
       <c r="E6" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1909,8 +1969,17 @@
       <c r="E7" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1923,8 +1992,11 @@
       <c r="E8" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H8" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1937,8 +2009,11 @@
       <c r="E9" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H9" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1951,8 +2026,11 @@
       <c r="E10" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H10" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1965,8 +2043,11 @@
       <c r="E11" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H11" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1979,8 +2060,11 @@
       <c r="E12" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H12" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1993,8 +2077,11 @@
       <c r="E13" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H13" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2007,8 +2094,11 @@
       <c r="E14" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H14" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2021,8 +2111,11 @@
       <c r="E15" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H15" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2035,8 +2128,11 @@
       <c r="E16" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H16" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2049,8 +2145,11 @@
       <c r="E17" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H17" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2063,8 +2162,11 @@
       <c r="E18" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2077,8 +2179,11 @@
       <c r="E19" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H19" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -2097,8 +2202,14 @@
       <c r="F20" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2117,8 +2228,14 @@
       <c r="F21" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2132,7 +2249,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -2146,7 +2263,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -2160,7 +2277,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2174,7 +2291,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -2188,7 +2305,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -2202,7 +2319,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -2216,7 +2333,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -2230,7 +2347,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -2244,7 +2361,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2258,7 +2375,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -2272,7 +2389,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -2286,7 +2403,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -2300,7 +2417,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2314,7 +2431,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -2328,7 +2445,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -2342,7 +2459,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -2356,7 +2473,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -2370,7 +2487,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -2389,8 +2506,14 @@
       <c r="F40" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G40" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2409,8 +2532,14 @@
       <c r="F41" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G41" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2424,7 +2553,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2438,7 +2567,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2452,7 +2581,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2466,7 +2595,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2480,7 +2609,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2494,7 +2623,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2508,7 +2637,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2522,7 +2651,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2536,7 +2665,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2550,7 +2679,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2564,7 +2693,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2578,7 +2707,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2592,7 +2721,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2606,7 +2735,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2620,7 +2749,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2634,7 +2763,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2648,7 +2777,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2662,7 +2791,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2681,8 +2810,14 @@
       <c r="F60" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G60" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2701,8 +2836,14 @@
       <c r="F61" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G61" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2716,7 +2857,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2730,7 +2871,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2744,7 +2885,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2758,7 +2899,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2772,7 +2913,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2786,7 +2927,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2800,7 +2941,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2814,7 +2955,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2828,7 +2969,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2842,7 +2983,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2856,7 +2997,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2870,7 +3011,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2884,7 +3025,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2898,7 +3039,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2912,7 +3053,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2926,7 +3067,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2940,7 +3081,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2954,7 +3095,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2973,8 +3114,14 @@
       <c r="F80" s="2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G80" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -2990,8 +3137,17 @@
       <c r="E81" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F81" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -3005,7 +3161,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -3019,7 +3175,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -3033,7 +3189,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -3047,7 +3203,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -3061,7 +3217,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -3075,7 +3231,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -3089,7 +3245,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -3103,7 +3259,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>179</v>
       </c>
@@ -3117,7 +3273,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -3131,7 +3287,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -3145,7 +3301,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -3159,7 +3315,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -3173,7 +3329,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>189</v>
       </c>
@@ -3187,7 +3343,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -3201,7 +3357,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -3215,7 +3371,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -3229,7 +3385,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -3243,7 +3399,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -3259,8 +3415,17 @@
       <c r="E100" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F100" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -3276,8 +3441,17 @@
       <c r="E101" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -3291,7 +3465,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>205</v>
       </c>
@@ -3305,7 +3479,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>207</v>
       </c>
@@ -3319,7 +3493,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>209</v>
       </c>
@@ -3333,7 +3507,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -3347,7 +3521,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -3361,7 +3535,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -3375,7 +3549,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -3389,7 +3563,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>219</v>
       </c>
@@ -3403,7 +3577,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -3417,7 +3591,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>223</v>
       </c>
@@ -3431,7 +3605,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -3445,7 +3619,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -3459,7 +3633,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -3473,7 +3647,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -3487,7 +3661,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -3501,7 +3675,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -3515,7 +3689,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -3529,7 +3703,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -3545,8 +3719,17 @@
       <c r="E120" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F120" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -3562,8 +3745,17 @@
       <c r="E121" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F121" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -3577,7 +3769,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -3591,7 +3783,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -3605,7 +3797,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3619,7 +3811,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -3633,7 +3825,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3647,7 +3839,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -3661,7 +3853,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -3675,7 +3867,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -3689,7 +3881,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -3703,7 +3895,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -3717,7 +3909,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3731,7 +3923,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3745,7 +3937,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3759,7 +3951,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3773,7 +3965,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3787,7 +3979,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3801,7 +3993,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3815,7 +4007,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -3831,8 +4023,17 @@
       <c r="E140" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F140" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3848,8 +4049,17 @@
       <c r="E141" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F141" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -3863,7 +4073,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -3877,7 +4087,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -3891,7 +4101,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>289</v>
       </c>
@@ -3905,7 +4115,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>291</v>
       </c>
@@ -3919,7 +4129,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>293</v>
       </c>
@@ -3933,7 +4143,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>295</v>
       </c>
@@ -3947,7 +4157,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>297</v>
       </c>
@@ -3961,7 +4171,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>299</v>
       </c>
@@ -3975,7 +4185,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>301</v>
       </c>
@@ -3989,7 +4199,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>303</v>
       </c>
@@ -4003,7 +4213,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>305</v>
       </c>
@@ -4017,7 +4227,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>307</v>
       </c>
@@ -4031,7 +4241,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>309</v>
       </c>
@@ -4045,7 +4255,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>311</v>
       </c>
@@ -4059,7 +4269,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -4073,7 +4283,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>315</v>
       </c>
@@ -4087,7 +4297,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>317</v>
       </c>
@@ -4101,7 +4311,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>319</v>
       </c>
@@ -4117,8 +4327,17 @@
       <c r="E160" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F160" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>321</v>
       </c>
@@ -4134,8 +4353,17 @@
       <c r="E161" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F161" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>323</v>
       </c>
@@ -4149,7 +4377,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>325</v>
       </c>
@@ -4163,7 +4391,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>327</v>
       </c>
@@ -4177,7 +4405,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -4191,7 +4419,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>331</v>
       </c>
@@ -4205,7 +4433,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>333</v>
       </c>
@@ -4219,7 +4447,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>335</v>
       </c>
@@ -4233,7 +4461,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>337</v>
       </c>
@@ -4247,7 +4475,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>339</v>
       </c>
@@ -4261,7 +4489,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>341</v>
       </c>
@@ -4275,7 +4503,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>343</v>
       </c>
@@ -4289,7 +4517,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>345</v>
       </c>
@@ -4303,7 +4531,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -4317,7 +4545,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -4331,7 +4559,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -4345,7 +4573,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>353</v>
       </c>
@@ -4359,7 +4587,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>355</v>
       </c>
@@ -4373,7 +4601,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>357</v>
       </c>
@@ -4387,7 +4615,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -4403,8 +4631,17 @@
       <c r="E180" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F180" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -4420,8 +4657,17 @@
       <c r="E181" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F181" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>363</v>
       </c>
@@ -4435,7 +4681,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>365</v>
       </c>
@@ -4449,7 +4695,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>367</v>
       </c>
@@ -4463,7 +4709,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>369</v>
       </c>
@@ -4477,7 +4723,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>371</v>
       </c>
@@ -4491,7 +4737,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>373</v>
       </c>
@@ -4505,7 +4751,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>375</v>
       </c>
@@ -4519,7 +4765,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>377</v>
       </c>
@@ -4533,7 +4779,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>379</v>
       </c>
@@ -4547,7 +4793,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>381</v>
       </c>
@@ -4561,7 +4807,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>383</v>
       </c>
@@ -4575,7 +4821,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>385</v>
       </c>
@@ -4589,7 +4835,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>387</v>
       </c>
@@ -4603,7 +4849,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>389</v>
       </c>
@@ -4617,7 +4863,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>391</v>
       </c>
@@ -4631,7 +4877,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>393</v>
       </c>
@@ -4645,7 +4891,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>395</v>
       </c>
@@ -4659,7 +4905,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>397</v>
       </c>
@@ -4673,7 +4919,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>399</v>
       </c>
@@ -4689,8 +4935,17 @@
       <c r="E200" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F200" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>401</v>
       </c>
@@ -4706,8 +4961,17 @@
       <c r="E201" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F201" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>403</v>
       </c>
@@ -4721,7 +4985,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>405</v>
       </c>
@@ -4735,7 +4999,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>407</v>
       </c>
@@ -4749,7 +5013,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>409</v>
       </c>
@@ -4763,7 +5027,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>411</v>
       </c>
@@ -4777,7 +5041,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>413</v>
       </c>
@@ -4791,7 +5055,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>415</v>
       </c>
@@ -4960,6 +5224,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/code/data/coursedata.xlsx
+++ b/code/data/coursedata.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MyAccount/Documents/_Development/generateCorporateCoursedata/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7C7341-6C55-964B-9093-6CCEBB376103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED14973-939F-CF45-8772-032167528959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="1820" windowWidth="25520" windowHeight="17320" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29160" windowHeight="18980" xr2:uid="{6615DF46-4F27-2346-A964-154937608818}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$220</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="470">
   <si>
     <t>Over-Reliance on AI (Automation Bias)</t>
   </si>
@@ -1407,6 +1410,45 @@
   </si>
   <si>
     <t>Batch 2</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>Audio Rec'd</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
+    <t>Batch 3</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Pre Edit Done</t>
+  </si>
+  <si>
+    <t>Course Build</t>
+  </si>
+  <si>
+    <t>Video Edit</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1841,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
-  <dimension ref="A1:H219"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.6640625" customWidth="1"/>
@@ -1807,40 +1850,48 @@
     <col min="3" max="3" width="35.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>38</v>
@@ -1860,13 +1911,16 @@
       <c r="H2" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>38</v>
@@ -1886,19 +1940,28 @@
       <c r="H3" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>449</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>453</v>
@@ -1907,15 +1970,21 @@
         <v>454</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>38</v>
@@ -1933,12 +2002,12 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>38</v>
@@ -1956,12 +2025,12 @@
         <v>456</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
@@ -1979,12 +2048,12 @@
         <v>456</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>38</v>
@@ -1992,16 +2061,22 @@
       <c r="E8" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>38</v>
@@ -2009,16 +2084,22 @@
       <c r="E9" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>38</v>
@@ -2026,16 +2107,22 @@
       <c r="E10" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>38</v>
@@ -2043,16 +2130,22 @@
       <c r="E11" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>38</v>
@@ -2060,16 +2153,22 @@
       <c r="E12" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>38</v>
@@ -2077,16 +2176,22 @@
       <c r="E13" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H13" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>38</v>
@@ -2094,16 +2199,22 @@
       <c r="E14" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H14" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>38</v>
@@ -2111,16 +2222,22 @@
       <c r="E15" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F15" t="s">
+        <v>453</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H15" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>38</v>
@@ -2128,16 +2245,22 @@
       <c r="E16" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F16" t="s">
+        <v>453</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H16" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>38</v>
@@ -2145,16 +2268,22 @@
       <c r="E17" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F17" t="s">
+        <v>453</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H17" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>38</v>
@@ -2162,16 +2291,22 @@
       <c r="E18" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F18" t="s">
+        <v>453</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H18" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
@@ -2179,42 +2314,45 @@
       <c r="E19" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="F19" t="s">
+        <v>453</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>451</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F20" t="s">
         <v>453</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>454</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>439</v>
@@ -2234,27 +2372,51 @@
       <c r="H21" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>439</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E22" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>439</v>
@@ -2262,13 +2424,22 @@
       <c r="E23" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>439</v>
@@ -2276,13 +2447,22 @@
       <c r="E24" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F24" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>439</v>
@@ -2291,12 +2471,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>439</v>
@@ -2305,12 +2485,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>439</v>
@@ -2319,12 +2499,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>439</v>
@@ -2333,12 +2513,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>439</v>
@@ -2347,12 +2527,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>439</v>
@@ -2361,12 +2541,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>439</v>
@@ -2375,12 +2555,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>439</v>
@@ -2389,12 +2569,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>439</v>
@@ -2403,12 +2583,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>439</v>
@@ -2417,12 +2597,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>439</v>
@@ -2431,12 +2611,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>439</v>
@@ -2445,12 +2625,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>439</v>
@@ -2459,12 +2639,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>439</v>
@@ -2473,12 +2653,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>439</v>
@@ -2487,38 +2667,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>79</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>80</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>440</v>
@@ -2538,27 +2706,45 @@
       <c r="H41" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>440</v>
       </c>
+      <c r="D42" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E42" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>440</v>
@@ -2567,12 +2753,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>440</v>
@@ -2581,12 +2767,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>440</v>
@@ -2595,12 +2781,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>440</v>
@@ -2609,12 +2795,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>440</v>
@@ -2623,12 +2809,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>440</v>
@@ -2637,12 +2823,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>440</v>
@@ -2651,12 +2837,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>440</v>
@@ -2665,12 +2851,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>440</v>
@@ -2679,12 +2865,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>440</v>
@@ -2693,12 +2879,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>440</v>
@@ -2707,12 +2893,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>440</v>
@@ -2721,12 +2907,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>440</v>
@@ -2735,12 +2921,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>440</v>
@@ -2749,12 +2935,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>440</v>
@@ -2763,12 +2949,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>440</v>
@@ -2777,12 +2963,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>440</v>
@@ -2791,38 +2977,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>119</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>120</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" t="s">
-        <v>122</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>441</v>
@@ -2842,27 +3016,45 @@
       <c r="H61" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>441</v>
       </c>
+      <c r="D62" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E62" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>441</v>
@@ -2871,12 +3063,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>441</v>
@@ -2885,12 +3077,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>441</v>
@@ -2899,12 +3091,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>441</v>
@@ -2913,12 +3105,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>441</v>
@@ -2927,12 +3119,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>441</v>
@@ -2941,12 +3133,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B69" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>441</v>
@@ -2955,12 +3147,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>441</v>
@@ -2969,12 +3161,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>441</v>
@@ -2983,12 +3175,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>441</v>
@@ -2997,12 +3189,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>441</v>
@@ -3011,12 +3203,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>441</v>
@@ -3025,12 +3217,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>441</v>
@@ -3039,12 +3231,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>441</v>
@@ -3053,12 +3245,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>441</v>
@@ -3067,12 +3259,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>441</v>
@@ -3081,12 +3273,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>441</v>
@@ -3095,38 +3287,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>159</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>160</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B81" t="s">
-        <v>162</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>442</v>
@@ -3146,27 +3326,51 @@
       <c r="H81" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="D82" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E82" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>442</v>
@@ -3175,12 +3379,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>442</v>
@@ -3189,12 +3393,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>442</v>
@@ -3203,12 +3407,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>442</v>
@@ -3217,12 +3421,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>442</v>
@@ -3231,12 +3435,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>442</v>
@@ -3245,12 +3449,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>442</v>
@@ -3259,12 +3463,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>442</v>
@@ -3273,12 +3477,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>442</v>
@@ -3287,12 +3491,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>442</v>
@@ -3301,12 +3505,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>442</v>
@@ -3315,12 +3519,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>442</v>
@@ -3329,12 +3533,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>442</v>
@@ -3343,12 +3547,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>442</v>
@@ -3357,12 +3561,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>442</v>
@@ -3371,12 +3575,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>442</v>
@@ -3385,12 +3589,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>442</v>
@@ -3399,38 +3603,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
         <v>200</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>201</v>
-      </c>
-      <c r="B101" t="s">
-        <v>202</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>443</v>
@@ -3450,27 +3642,51 @@
       <c r="H101" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I101" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B102" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="D102" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E102" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>443</v>
@@ -3479,12 +3695,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>443</v>
@@ -3493,12 +3709,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>443</v>
@@ -3507,12 +3723,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>443</v>
@@ -3521,12 +3737,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>443</v>
@@ -3535,12 +3751,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>443</v>
@@ -3549,12 +3765,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B109" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>443</v>
@@ -3563,12 +3779,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B110" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>443</v>
@@ -3577,12 +3793,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B111" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>443</v>
@@ -3591,12 +3807,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B112" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>443</v>
@@ -3605,12 +3821,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B113" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>443</v>
@@ -3619,12 +3835,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>443</v>
@@ -3633,12 +3849,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B115" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>443</v>
@@ -3647,12 +3863,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B116" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>443</v>
@@ -3661,12 +3877,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B117" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>443</v>
@@ -3675,12 +3891,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B118" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>443</v>
@@ -3689,12 +3905,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B119" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>443</v>
@@ -3703,38 +3919,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>239</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>240</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>241</v>
-      </c>
-      <c r="B121" t="s">
-        <v>242</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>444</v>
@@ -3754,27 +3958,45 @@
       <c r="H121" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I121" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="D122" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E122" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B123" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>444</v>
@@ -3783,12 +4005,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>444</v>
@@ -3797,12 +4019,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B125" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>444</v>
@@ -3811,12 +4033,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>444</v>
@@ -3825,12 +4047,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>444</v>
@@ -3839,12 +4061,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B128" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>444</v>
@@ -3853,12 +4075,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>444</v>
@@ -3867,12 +4089,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B130" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>444</v>
@@ -3881,12 +4103,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>444</v>
@@ -3895,12 +4117,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B132" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>444</v>
@@ -3909,12 +4131,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>444</v>
@@ -3923,12 +4145,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B134" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>444</v>
@@ -3937,12 +4159,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B135" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>444</v>
@@ -3951,12 +4173,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B136" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>444</v>
@@ -3965,12 +4187,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B137" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>444</v>
@@ -3979,12 +4201,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>444</v>
@@ -3993,12 +4215,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>444</v>
@@ -4007,38 +4229,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>277</v>
+      </c>
+      <c r="B140" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
         <v>279</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B141" t="s">
         <v>280</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>281</v>
-      </c>
-      <c r="B141" t="s">
-        <v>282</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>445</v>
@@ -4058,27 +4268,45 @@
       <c r="H141" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I141" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>445</v>
       </c>
+      <c r="D142" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E142" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>445</v>
@@ -4087,12 +4315,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>445</v>
@@ -4101,12 +4329,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B145" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>445</v>
@@ -4115,12 +4343,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>445</v>
@@ -4129,12 +4357,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B147" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>445</v>
@@ -4143,12 +4371,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B148" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>445</v>
@@ -4157,12 +4385,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B149" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>445</v>
@@ -4171,12 +4399,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B150" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>445</v>
@@ -4185,12 +4413,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B151" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>445</v>
@@ -4199,12 +4427,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B152" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>445</v>
@@ -4213,12 +4441,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B153" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>445</v>
@@ -4227,12 +4455,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B154" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>445</v>
@@ -4241,12 +4469,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B155" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>445</v>
@@ -4255,12 +4483,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>445</v>
@@ -4269,12 +4497,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B157" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>445</v>
@@ -4283,12 +4511,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>445</v>
@@ -4297,12 +4525,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B159" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>445</v>
@@ -4311,43 +4539,31 @@
         <v>452</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
+        <v>317</v>
+      </c>
+      <c r="B160" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>319</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>320</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H160" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>321</v>
-      </c>
-      <c r="B161" t="s">
-        <v>322</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D161" s="1" t="s">
         <v>451</v>
       </c>
       <c r="E161" s="1" t="s">
@@ -4362,27 +4578,45 @@
       <c r="H161" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I161" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="D162" s="2" t="s">
+        <v>451</v>
+      </c>
       <c r="E162" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B163" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>446</v>
@@ -4391,12 +4625,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B164" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>446</v>
@@ -4405,12 +4639,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B165" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>446</v>
@@ -4419,12 +4653,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B166" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>446</v>
@@ -4433,12 +4667,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B167" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>446</v>
@@ -4447,12 +4681,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B168" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>446</v>
@@ -4461,12 +4695,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B169" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>446</v>
@@ -4475,12 +4709,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B170" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>446</v>
@@ -4489,12 +4723,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>446</v>
@@ -4503,12 +4737,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B172" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>446</v>
@@ -4517,12 +4751,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B173" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>446</v>
@@ -4531,12 +4765,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B174" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>446</v>
@@ -4545,12 +4779,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>446</v>
@@ -4559,12 +4793,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>446</v>
@@ -4573,12 +4807,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B177" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>446</v>
@@ -4587,12 +4821,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B178" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>446</v>
@@ -4601,12 +4835,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B179" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>446</v>
@@ -4615,38 +4849,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>357</v>
+      </c>
+      <c r="B180" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
         <v>359</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B181" t="s">
         <v>360</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H180" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>361</v>
-      </c>
-      <c r="B181" t="s">
-        <v>362</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>447</v>
@@ -4666,27 +4888,45 @@
       <c r="H181" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I181" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B182" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>447</v>
       </c>
+      <c r="D182" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="E182" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B183" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>447</v>
@@ -4695,12 +4935,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>447</v>
@@ -4709,12 +4949,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B185" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>447</v>
@@ -4723,12 +4963,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>447</v>
@@ -4737,12 +4977,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B187" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>447</v>
@@ -4751,12 +4991,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B188" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>447</v>
@@ -4765,12 +5005,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B189" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>447</v>
@@ -4779,12 +5019,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B190" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>447</v>
@@ -4793,12 +5033,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B191" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>447</v>
@@ -4807,12 +5047,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B192" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>447</v>
@@ -4821,12 +5061,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>447</v>
@@ -4835,12 +5075,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>447</v>
@@ -4849,12 +5089,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B195" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>447</v>
@@ -4863,12 +5103,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B196" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>447</v>
@@ -4877,12 +5117,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B197" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>447</v>
@@ -4891,12 +5131,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>447</v>
@@ -4905,12 +5145,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B199" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>447</v>
@@ -4919,38 +5159,26 @@
         <v>452</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>397</v>
+      </c>
+      <c r="B200" t="s">
+        <v>398</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
         <v>399</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B201" t="s">
         <v>400</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
-        <v>401</v>
-      </c>
-      <c r="B201" t="s">
-        <v>402</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>448</v>
@@ -4970,27 +5198,51 @@
       <c r="H201" s="2" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I201" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J201" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B202" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>448</v>
       </c>
+      <c r="D202" s="1" t="s">
+        <v>449</v>
+      </c>
       <c r="E202" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B203" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>448</v>
@@ -4999,12 +5251,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B204" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>448</v>
@@ -5013,12 +5265,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>448</v>
@@ -5027,12 +5279,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>448</v>
@@ -5041,12 +5293,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>448</v>
@@ -5055,12 +5307,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B208" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>448</v>
@@ -5069,12 +5321,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>448</v>
@@ -5083,12 +5335,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B210" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>448</v>
@@ -5097,12 +5349,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>448</v>
@@ -5111,12 +5363,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>448</v>
@@ -5125,12 +5377,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B213" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>448</v>
@@ -5139,12 +5391,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>448</v>
@@ -5153,12 +5405,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>448</v>
@@ -5167,12 +5419,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>448</v>
@@ -5181,12 +5433,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>448</v>
@@ -5195,12 +5447,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B218" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>448</v>
@@ -5209,12 +5461,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B219" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>448</v>
@@ -5223,7 +5475,29 @@
         <v>452</v>
       </c>
     </row>
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>437</v>
+      </c>
+      <c r="B220" t="s">
+        <v>438</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:H220" xr:uid="{26774B9C-3336-954A-A560-78C4EE833A9D}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Batch 1"/>
+        <filter val="Batch 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
